--- a/output/pdf_financials_xlsx/NPTH.xlsx
+++ b/output/pdf_financials_xlsx/NPTH.xlsx
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>1.127</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>1.372</v>
       </c>
     </row>
     <row r="71">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.091</v>
+        <v>4.218</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.441</v>
+        <v>4.813</v>
       </c>
     </row>
     <row r="72">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.277</v>
+        <v>0.15</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.983</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="76">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1567115551694179</v>
+        <v>0.1975094121054156</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.1830429732868757</v>
+        <v>0.2361595044521874</v>
       </c>
     </row>
     <row r="81">
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="117">
@@ -3392,7 +3392,11 @@
           <t>Current portion of lease obligations 15</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4826,7 +4830,11 @@
           <t>Deferred income tax recovery 24</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -4950,7 +4958,11 @@
           <t>Acquisition of intangible assets, net 12</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
